--- a/Equipo/Equipo.xlsx
+++ b/Equipo/Equipo.xlsx
@@ -1,25 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanl\GitHub\Proyecto-IDS\Equipo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1F7871-DEFF-498A-912F-EE7809C40B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-28920" yWindow="-375" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Table2[#All]</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="79">
   <si>
     <t>Nombre</t>
   </si>
@@ -27,35 +44,35 @@
     <t>Email</t>
   </si>
   <si>
-    <t xml:space="preserve">¿Vinculado/a a Universidad El Bosque? (escribir "Sí" o  "No")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalafón (solo si tiene vinculación  a UEB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupo de Investigación UEB (solo si tiene vinculación  a UEB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afiliación (puede ser independiente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas de dedicación al proyecto (si tiene vinculación  a UEB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Área de experticia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoja de Vida
+    <t>¿Vinculado/a a Universidad El Bosque? (escribir "Sí" o  "No")</t>
+  </si>
+  <si>
+    <t>Escalafón (solo si tiene vinculación  a UEB)</t>
+  </si>
+  <si>
+    <t>Grupo de Investigación UEB (solo si tiene vinculación  a UEB)</t>
+  </si>
+  <si>
+    <t>Afiliación (puede ser independiente)</t>
+  </si>
+  <si>
+    <t>Horas de dedicación al proyecto (si tiene vinculación  a UEB)</t>
+  </si>
+  <si>
+    <t>Área de experticia</t>
+  </si>
+  <si>
+    <t>Hoja de Vida
 (agregar PDF a esta carpeta)</t>
   </si>
   <si>
-    <t xml:space="preserve">Experticia y formación relevantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funciones en el proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan David Leongómez Peña</t>
+    <t>Experticia y formación relevantes</t>
+  </si>
+  <si>
+    <t>Funciones en el proyecto</t>
+  </si>
+  <si>
+    <t>Juan David Leongómez Peña</t>
   </si>
   <si>
     <t>jleongomez@unbosque.edu.co</t>
@@ -64,32 +81,32 @@
     <t>Sí</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesor Asociado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CODEC: Ciencias Cognitivas y del Comportamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facultad de Psicología
+    <t>Profesor Asociado</t>
+  </si>
+  <si>
+    <t>CODEC: Ciencias Cognitivas y del Comportamiento</t>
+  </si>
+  <si>
+    <t>Facultad de Psicología
 Universidad El Bosque</t>
   </si>
   <si>
-    <t xml:space="preserve">Análisis de comportamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctor en psicología con énfasis en ciencias evolutivas del comportamiento, experto en modulación vocal, análisis acústico y modelado estadístico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diseño, análisis y modelado estadístico, manipulación acústica, análisis acústico, dirección general, coordinación, supervisión de análisis, escritura de publicaciones y actividades de divulgación.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milena Vásquez-Amézquita</t>
+    <t>Análisis de comportamiento</t>
+  </si>
+  <si>
+    <t>Doctor en psicología con énfasis en ciencias evolutivas del comportamiento, experto en modulación vocal, análisis acústico y modelado estadístico.</t>
+  </si>
+  <si>
+    <t>Diseño, análisis y modelado estadístico, manipulación acústica, análisis acústico, dirección general, coordinación, supervisión de análisis, escritura de publicaciones y actividades de divulgación.</t>
+  </si>
+  <si>
+    <t>Milena Vásquez-Amézquita</t>
   </si>
   <si>
     <t>mvasquezam@unbosque.edu.co</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesor Asociada</t>
+    <t>Profesor Asociada</t>
   </si>
   <si>
     <t>Neurociencia</t>
@@ -119,50 +136,50 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Coordinación de estudios con eye-tracking, apoyo en análisis, supervisión de semillero SexCog y 1 trabajo de grado, publicaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicolás Ignacio Ramos Rodríguez</t>
+    <t>Coordinación de estudios con eye-tracking, apoyo en análisis, supervisión de semillero SexCog y 1 trabajo de grado, publicaciones.</t>
+  </si>
+  <si>
+    <t>Nicolás Ignacio Ramos Rodríguez</t>
   </si>
   <si>
     <t>ramosnicolas@unbosque.edu.co</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesor Titular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investigaciones Pediátricas Bosque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facultad de Medicina
+    <t>Profesor Titular</t>
+  </si>
+  <si>
+    <t>Investigaciones Pediátricas Bosque</t>
+  </si>
+  <si>
+    <t>Facultad de Medicina
 Universidad El Bosque</t>
   </si>
   <si>
     <t>Pediatría</t>
   </si>
   <si>
-    <t xml:space="preserve">Propuestas de posibles aplicaciones clínicas y/o recomendaciones a cuidadores de bebés a partir de resultados. Reclutamiento de participantes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Catalina Bages Mesa</t>
+    <t>Propuestas de posibles aplicaciones clínicas y/o recomendaciones a cuidadores de bebés a partir de resultados. Reclutamiento de participantes.</t>
+  </si>
+  <si>
+    <t>María Catalina Bages Mesa</t>
   </si>
   <si>
     <t>bagesmaria@unbosque.edu.co</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesora Titular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Médica pediatra y nutrióloga pediatra, magíster en Nutrición Clínica Pediátrica, experta en pediatría, nutrición infantil y salud materno-infantil.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bertha Patricia Calderón Ortiz</t>
+    <t>Profesora Titular</t>
+  </si>
+  <si>
+    <t>Médica pediatra y nutrióloga pediatra, magíster en Nutrición Clínica Pediátrica, experta en pediatría, nutrición infantil y salud materno-infantil.</t>
+  </si>
+  <si>
+    <t>Bertha Patricia Calderón Ortiz</t>
   </si>
   <si>
     <t>bercalde@unbosque.edu.co</t>
   </si>
   <si>
-    <t xml:space="preserve">Daniel Toro Avila</t>
+    <t>Daniel Toro Avila</t>
   </si>
   <si>
     <t>dtoroavila@gmail.com</t>
@@ -177,13 +194,13 @@
     <t>Independiente</t>
   </si>
   <si>
-    <t xml:space="preserve">Adriana María Cristancho Arévalo</t>
+    <t>Adriana María Cristancho Arévalo</t>
   </si>
   <si>
     <t>adrianacristancho81@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Ruth Stella Chacon Pinilla</t>
+    <t>Ruth Stella Chacon Pinilla</t>
   </si>
   <si>
     <t>chaconruth@unbosque.edu.co</t>
@@ -192,10 +209,10 @@
     <t xml:space="preserve">Profesora Titular </t>
   </si>
   <si>
-    <t xml:space="preserve">Educación e Investigación UNBOSQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facultad de Educación
+    <t>Educación e Investigación UNBOSQUE</t>
+  </si>
+  <si>
+    <t>Facultad de Educación
 Universidad El Bosque</t>
   </si>
   <si>
@@ -205,138 +222,148 @@
     <t xml:space="preserve">Doctora en Educación. Líneas de trabajo infancia, desarrollo y aprendizaje. Familia y escuela. </t>
   </si>
   <si>
-    <t xml:space="preserve">Apoyo teórico en educación infantil, supervisión estudiante de maestría, actividades de divulgación, publicaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lina Maria Rodríguez Granada</t>
+    <t>Apoyo teórico en educación infantil, supervisión estudiante de maestría, actividades de divulgación, publicaciones.</t>
+  </si>
+  <si>
+    <t>Lina Maria Rodríguez Granada</t>
   </si>
   <si>
     <t>rodriguezlina@unbosque.edu.co</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesora Asistente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psicología de la salud, del deporte y clínica</t>
+    <t>Profesora Asistente</t>
+  </si>
+  <si>
+    <t>Psicología de la salud, del deporte y clínica</t>
   </si>
   <si>
     <t>Música</t>
   </si>
   <si>
-    <t xml:space="preserve">Magíster en Psicología y especialista en Psicología del Deporte,docente de apoyo del semillero Muísca y Psicología.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bases teóricas desde psicología de la música, supervisión semillero Música y Psicología, actividades de divulgación, apoyo en análisis de Estudio 2 y publicaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luz Helena Buitrago León</t>
+    <t>Magíster en Psicología y especialista en Psicología del Deporte,docente de apoyo del semillero Muísca y Psicología.</t>
+  </si>
+  <si>
+    <t>Bases teóricas desde psicología de la música, supervisión semillero Música y Psicología, actividades de divulgación, apoyo en análisis de Estudio 2 y publicaciones.</t>
+  </si>
+  <si>
+    <t>Luz Helena Buitrago León</t>
   </si>
   <si>
     <t>buitragoluz@unbosque.edu.co</t>
   </si>
   <si>
-    <t xml:space="preserve">Psicología del desarrollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magíster en Psicología y especialista en Docencia Universitaria, con doctorado en Ciencias de la Salud en curso; experta en desarrollo infantil, psicología clínica y resiliencia familiar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoyo teórico en desarrollo infantil, supervisión estudiante de especialización, actividades de divulgación, publicaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natalia Moreno-Buitrago</t>
+    <t>Psicología del desarrollo</t>
+  </si>
+  <si>
+    <t>Magíster en Psicología y especialista en Docencia Universitaria, con doctorado en Ciencias de la Salud en curso; experta en desarrollo infantil, psicología clínica y resiliencia familiar.</t>
+  </si>
+  <si>
+    <t>Apoyo teórico en desarrollo infantil, supervisión estudiante de especialización, actividades de divulgación, publicaciones.</t>
+  </si>
+  <si>
+    <t>Natalia Moreno-Buitrago</t>
   </si>
   <si>
     <t>morenobuitrago.1@buckeyemail.osu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Candidata Doctoral
+    <t>Candidata Doctoral
 School of Music
 Ohio State University
 Estados Unidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Desarrollo musical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bióloga y pedagoga musical. En su doctorado estudia el desarrollo de los comportamientos musicales y cómo se moldean desde la infancia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoyo para la medición de habilidades musicales y lingüísticas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David A. Puts</t>
+    <t>Desarrollo musical</t>
+  </si>
+  <si>
+    <t>Bióloga y pedagoga musical. En su doctorado estudia el desarrollo de los comportamientos musicales y cómo se moldean desde la infancia.</t>
+  </si>
+  <si>
+    <t>Apoyo para la medición de habilidades musicales y lingüísticas</t>
+  </si>
+  <si>
+    <t>David A. Puts</t>
   </si>
   <si>
     <t>dap27@psu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesor Titular
+    <t>Profesor Titular
 Departamentio de Antropología
 Pennsylvania State University
 Estados Unidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Evolución comportamental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctor en antropología biológica, experto en endocrinología comportamental, evolución comportamental, y diferencias de sexo en humanos, con énfasis en análisis acústico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoyo al diseño general, análisis y manipulación acústica</t>
+    <t>Evolución comportamental</t>
+  </si>
+  <si>
+    <t>Doctor en antropología biológica, experto en endocrinología comportamental, evolución comportamental, y diferencias de sexo en humanos, con énfasis en análisis acústico.</t>
+  </si>
+  <si>
+    <t>Apoyo al diseño general, análisis y manipulación acústica</t>
+  </si>
+  <si>
+    <t>Instructora Asociada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9.000000"/>
+      <sz val="9"/>
       <color indexed="65"/>
       <name val="Aptos"/>
     </font>
     <font>
       <u/>
-      <sz val="9.000000"/>
+      <sz val="9"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="8.000000"/>
+      <sz val="8"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.000000"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.000000"/>
+      <sz val="8"/>
       <color indexed="64"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.000000"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -350,13 +377,12 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="solid"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -367,6 +393,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -377,16 +404,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -395,18 +423,18 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -421,78 +449,122 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="2" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="3" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="5" borderId="3" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="6" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
+        <sz val="8"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
@@ -512,7 +584,191 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color indexed="64"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color indexed="64"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -522,7 +778,75 @@
         <strike val="0"/>
         <u/>
         <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
+        <sz val="8"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
         <color theme="10"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
@@ -533,7 +857,7 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" relativeIndent="0" shrinkToFit="0" readingOrder="0"/>
       <border>
         <left style="thin">
           <color auto="1"/>
@@ -547,277 +871,15 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <diagonal/>
-        <vertical style="none"/>
-        <horizontal style="none"/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="65"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="65"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-        <vertical style="none"/>
-        <horizontal style="none"/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
       <font>
         <strike val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <alignment horizontal="left" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <color indexed="64"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-        <vertical style="none"/>
-        <horizontal style="none"/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <alignment horizontal="left" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="65"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
-        <color indexed="64"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="65"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <diagonal/>
-        <vertical style="none"/>
-        <horizontal style="none"/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8.000000"/>
+        <sz val="8"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
@@ -837,7 +899,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <diagonal/>
       </border>
     </dxf>
   </dxfs>
@@ -854,318 +915,35 @@
 </file>
 
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{BFBF76A3-6B92-422A-A127-E7C554C462B6}">
-    <nsvFilter filterId="{47312F7A-547A-4F0B-93CB-2465DECF0052}" ref="A1:L13" tableId="1"/>
+    <nsvFilter filterId="{00000000-0009-0000-0100-000001000000}" ref="A1:K13" tableId="1"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table2" ref="A1:K13">
-  <autoFilter ref="A1:K13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:K13">
+  <autoFilter ref="A1:K13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="Nombre" dataDxfId="0"/>
-    <tableColumn id="2" name="Email" dataDxfId="1"/>
-    <tableColumn id="3" name="¿Vinculado/a a Universidad El Bosque? (escribir &quot;Sí&quot; o  &quot;No&quot;)" dataDxfId="2"/>
-    <tableColumn id="4" name="Escalafón (solo si tiene vinculación  a UEB)" dataDxfId="3"/>
-    <tableColumn id="5" name="Grupo de Investigación UEB (solo si tiene vinculación  a UEB)" dataDxfId="4"/>
-    <tableColumn id="6" name="Afiliación (puede ser independiente)" dataDxfId="5"/>
-    <tableColumn id="7" name="Horas de dedicación al proyecto (si tiene vinculación  a UEB)" dataDxfId="6"/>
-    <tableColumn id="8" name="Área de experticia" dataDxfId="7"/>
-    <tableColumn id="9" name="Hoja de Vida_x000a_(agregar PDF a esta carpeta)" dataDxfId="8"/>
-    <tableColumn id="10" name="Experticia y formación relevantes" dataDxfId="9"/>
-    <tableColumn id="11" name="Funciones en el proyecto" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nombre" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Email" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="¿Vinculado/a a Universidad El Bosque? (escribir &quot;Sí&quot; o  &quot;No&quot;)" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Escalafón (solo si tiene vinculación  a UEB)" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Grupo de Investigación UEB (solo si tiene vinculación  a UEB)" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Afiliación (puede ser independiente)" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Horas de dedicación al proyecto (si tiene vinculación  a UEB)" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Área de experticia" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Hoja de Vida_x000a_(agregar PDF a esta carpeta)" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Experticia y formación relevantes" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Funciones en el proyecto" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1356,26 +1134,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="19.42578125" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="19.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="23.140625"/>
-    <col customWidth="1" min="2" max="2" width="26.85546875"/>
-    <col customWidth="1" min="3" max="3" width="18.5703125"/>
-    <col customWidth="1" min="4" max="4" width="17"/>
-    <col customWidth="1" min="6" max="6" width="19.140625"/>
-    <col customWidth="1" min="7" max="7" width="18.140625"/>
-    <col customWidth="1" min="8" max="8" width="14.28515625"/>
-    <col customWidth="1" min="9" max="9" width="14.42578125"/>
-    <col customWidth="1" min="10" max="10" width="29.85546875"/>
-    <col customWidth="1" min="11" max="11" width="33.7109375"/>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="29.85546875" customWidth="1"/>
+    <col min="11" max="11" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45">
+    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1410,7 +1190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="56.25">
+    <row r="2" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -1445,7 +1225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" ht="33.75">
+    <row r="3" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>20</v>
       </c>
@@ -1480,7 +1260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="33.75">
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>26</v>
       </c>
@@ -1513,7 +1293,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" ht="45">
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>33</v>
       </c>
@@ -1524,7 +1304,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>29</v>
@@ -1548,7 +1328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" ht="33.75">
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>37</v>
       </c>
@@ -1558,8 +1338,8 @@
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
+      <c r="D6" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>29</v>
@@ -1581,7 +1361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="33.75">
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>39</v>
       </c>
@@ -1614,7 +1394,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="33.75">
+    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>44</v>
       </c>
@@ -1625,7 +1405,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>29</v>
@@ -1647,7 +1427,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="33.75">
+    <row r="9" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>46</v>
       </c>
@@ -1682,7 +1462,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" ht="45">
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>54</v>
       </c>
@@ -1717,7 +1497,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" ht="56.25">
+    <row r="11" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -1752,7 +1532,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" ht="45">
+    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>66</v>
       </c>
@@ -1787,7 +1567,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="58.5" customHeight="1">
+    <row r="13" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>72</v>
       </c>
@@ -1822,117 +1602,57 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="18"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:K13">
+    <cfRule type="containsBlanks" dxfId="3" priority="4">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C13">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",D2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Si">
+      <formula>NOT(ISERROR(SEARCH("Si",C2)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Sí"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I1"/>
-    <hyperlink r:id="rId2" ref="A2" tooltip="https://jdleongomez.info/es/"/>
-    <hyperlink r:id="rId3" ref="B2"/>
-    <hyperlink r:id="rId4" ref="A3" tooltip="https://scholar.google.es/citations?user=XgNEpfgAAAAJ"/>
-    <hyperlink r:id="rId5" ref="B3"/>
-    <hyperlink r:id="rId6" ref="A4" tooltip="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0000550124"/>
-    <hyperlink r:id="rId7" ref="B4"/>
-    <hyperlink r:id="rId8" ref="A5" tooltip="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0000004217"/>
-    <hyperlink r:id="rId9" ref="B5"/>
-    <hyperlink r:id="rId10" ref="A6" tooltip="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0000713171"/>
-    <hyperlink r:id="rId11" ref="B6"/>
-    <hyperlink r:id="rId12" ref="A7" tooltip="https://www.linkedin.com/in/danieltoroavilapediatra/?originalSubdomain=co"/>
-    <hyperlink r:id="rId13" ref="B7"/>
-    <hyperlink r:id="rId14" ref="A8" tooltip="https://www.linkedin.com/in/adriana-mar%C3%ADa-cristancho-ar%C3%A9valo-aa670354/?originalSubdomain=co"/>
-    <hyperlink r:id="rId15" ref="B8"/>
-    <hyperlink r:id="rId16" ref="A9"/>
-    <hyperlink r:id="rId17" ref="B9"/>
-    <hyperlink r:id="rId18" ref="A10"/>
-    <hyperlink r:id="rId19" ref="B10"/>
-    <hyperlink r:id="rId20" ref="A11"/>
-    <hyperlink r:id="rId21" ref="B11"/>
-    <hyperlink r:id="rId22" ref="A12" tooltip="https://music.osu.edu/people/morenobuitrago.1"/>
-    <hyperlink r:id="rId23" ref="B12"/>
-    <hyperlink r:id="rId24" ref="A13" tooltip="https://beel.la.psu.edu/labstaff/"/>
-    <hyperlink r:id="rId25" ref="B13"/>
+    <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A2" r:id="rId2" tooltip="https://jdleongomez.info/es/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A3" r:id="rId4" tooltip="https://scholar.google.es/citations?user=XgNEpfgAAAAJ" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A4" r:id="rId6" tooltip="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0000550124" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A5" r:id="rId8" tooltip="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0000004217" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B5" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A6" r:id="rId10" tooltip="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0000713171" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B6" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A7" r:id="rId12" tooltip="https://www.linkedin.com/in/danieltoroavilapediatra/?originalSubdomain=co" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B7" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A8" r:id="rId14" tooltip="https://www.linkedin.com/in/adriana-mar%C3%ADa-cristancho-ar%C3%A9valo-aa670354/?originalSubdomain=co" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B8" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B9" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="A10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B10" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="B11" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A12" r:id="rId22" tooltip="https://music.osu.edu/people/morenobuitrago.1" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B12" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="A13" r:id="rId24" tooltip="https://beel.la.psu.edu/labstaff/" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B13" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
   </hyperlinks>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="43" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="43" orientation="portrait"/>
   <tableParts count="1">
     <tablePart r:id="rId26"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsBlanks" priority="4" id="{00E200C2-00AD-4A43-9EE2-00E300D30013}">
-            <xm:f>LEN(TRIM(B2))=0</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:K13</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" text="Si" id="{00FA0047-004A-447B-8D32-000800200043}">
-            <xm:f>NOT(ISERROR(SEARCH("Si",C2)))</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF006100"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C2:C13</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{00AD003F-00B2-4248-8217-00D500FC0080}">
-            <xm:f>"Sí"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF006100"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C2:C13</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" text="No" id="{007C00CE-0044-4069-896A-008E00E1001C}">
-            <xm:f>NOT(ISERROR(SEARCH("No",D2)))</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C5700"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C2:C13</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>